--- a/รายชื่อพนักงานสำรวจอุบัติเหตุ (Update 1-8-69).xlsx
+++ b/รายชื่อพนักงานสำรวจอุบัติเหตุ (Update 1-8-69).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\i9\Desktop\se-survey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88BADF3C-3BBD-49B1-9427-DF0B7398C9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5B0CD9-424E-4AD2-9B72-66AEC7B07E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{ED29D988-C0B4-415C-8F81-34B95B357877}"/>
   </bookViews>
@@ -1166,9 +1166,6 @@
     <t>096-108-3031</t>
   </si>
   <si>
-    <t>SE478 นาย วรัญญู แสงแก้ว</t>
-  </si>
-  <si>
     <t>064-258-1761</t>
   </si>
   <si>
@@ -1377,6 +1374,9 @@
   </si>
   <si>
     <t>098-185-7888</t>
+  </si>
+  <si>
+    <t>SE478 นาย วรัญญู ยีนสุข</t>
   </si>
 </sst>
 </file>
@@ -2069,52 +2069,52 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2465,7 +2465,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="41" customFormat="1" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -2476,20 +2476,20 @@
       <c r="B3" s="85" t="s">
         <v>357</v>
       </c>
-      <c r="C3" s="106" t="s">
+      <c r="C3" s="94" t="s">
+        <v>412</v>
+      </c>
+      <c r="D3" s="96" t="s">
         <v>413</v>
-      </c>
-      <c r="D3" s="108" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="93"/>
       <c r="B4" s="86" t="s">
-        <v>436</v>
-      </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="109"/>
+        <v>435</v>
+      </c>
+      <c r="C4" s="95"/>
+      <c r="D4" s="97"/>
     </row>
     <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="43" t="s">
@@ -2507,11 +2507,11 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="68" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B6" s="69"/>
       <c r="C6" s="70" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D6" s="69"/>
     </row>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B18" s="17" t="s">
         <v>403</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>404</v>
       </c>
       <c r="D18" s="8"/>
     </row>
@@ -2727,7 +2727,7 @@
         <v>356</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D31" s="26" t="s">
         <v>359</v>
@@ -2749,11 +2749,11 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="63" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B33" s="12"/>
       <c r="C33" s="67" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D33" s="12"/>
     </row>
@@ -2964,26 +2964,26 @@
     </row>
     <row r="54" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="104" t="s">
+      <c r="A55" s="98" t="s">
         <v>156</v>
       </c>
       <c r="B55" s="88" t="s">
         <v>355</v>
       </c>
-      <c r="C55" s="102" t="s">
-        <v>424</v>
-      </c>
-      <c r="D55" s="100" t="s">
+      <c r="C55" s="100" t="s">
+        <v>423</v>
+      </c>
+      <c r="D55" s="102" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="105"/>
+      <c r="A56" s="99"/>
       <c r="B56" s="89" t="s">
-        <v>437</v>
-      </c>
-      <c r="C56" s="103"/>
-      <c r="D56" s="101"/>
+        <v>436</v>
+      </c>
+      <c r="C56" s="101"/>
+      <c r="D56" s="103"/>
     </row>
     <row r="57" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A57" s="43" t="s">
@@ -3001,11 +3001,11 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="68" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B58" s="69"/>
       <c r="C58" s="75" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D58" s="69"/>
     </row>
@@ -3163,11 +3163,11 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="71" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B71" s="80"/>
       <c r="C71" s="81" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D71" s="23"/>
     </row>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B75" s="19" t="s">
         <v>420</v>
-      </c>
-      <c r="B75" s="19" t="s">
-        <v>421</v>
       </c>
       <c r="C75" s="59" t="s">
         <v>184</v>
@@ -3277,11 +3277,11 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="71" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B80" s="80"/>
       <c r="C80" s="81" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D80" s="23"/>
     </row>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="B83" s="19" t="s">
         <v>422</v>
-      </c>
-      <c r="B83" s="19" t="s">
-        <v>423</v>
       </c>
       <c r="C83" s="59" t="s">
         <v>187</v>
@@ -3395,25 +3395,25 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="92" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B91" s="82" t="s">
-        <v>408</v>
-      </c>
-      <c r="C91" s="102" t="s">
+        <v>407</v>
+      </c>
+      <c r="C91" s="100" t="s">
         <v>361</v>
       </c>
-      <c r="D91" s="100" t="s">
+      <c r="D91" s="102" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A92" s="93"/>
       <c r="B92" s="83" t="s">
-        <v>438</v>
-      </c>
-      <c r="C92" s="103"/>
-      <c r="D92" s="101"/>
+        <v>437</v>
+      </c>
+      <c r="C92" s="101"/>
+      <c r="D92" s="103"/>
     </row>
     <row r="93" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A93" s="43" t="s">
@@ -3431,11 +3431,11 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="71" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B94" s="39"/>
       <c r="C94" s="72" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D94" s="39"/>
     </row>
@@ -3545,11 +3545,11 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="63" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B104" s="8"/>
       <c r="C104" s="67" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D104" s="8"/>
     </row>
@@ -3693,10 +3693,10 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="B116" s="17" t="s">
         <v>425</v>
-      </c>
-      <c r="B116" s="17" t="s">
-        <v>426</v>
       </c>
       <c r="C116" s="7" t="s">
         <v>171</v>
@@ -3837,26 +3837,26 @@
     </row>
     <row r="130" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A131" s="104" t="s">
+      <c r="A131" s="98" t="s">
         <v>160</v>
       </c>
       <c r="B131" s="88" t="s">
         <v>353</v>
       </c>
-      <c r="C131" s="98" t="s">
-        <v>406</v>
-      </c>
-      <c r="D131" s="96" t="s">
+      <c r="C131" s="104" t="s">
+        <v>405</v>
+      </c>
+      <c r="D131" s="106" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="105"/>
+      <c r="A132" s="99"/>
       <c r="B132" s="89" t="s">
-        <v>439</v>
-      </c>
-      <c r="C132" s="99"/>
-      <c r="D132" s="97"/>
+        <v>438</v>
+      </c>
+      <c r="C132" s="105"/>
+      <c r="D132" s="107"/>
     </row>
     <row r="133" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A133" s="43" t="s">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="B134" s="39"/>
       <c r="C134" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D134" s="8"/>
     </row>
@@ -3922,10 +3922,10 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B138" s="17" t="s">
         <v>427</v>
-      </c>
-      <c r="B138" s="17" t="s">
-        <v>428</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" s="17" t="s">
@@ -3990,7 +3990,7 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B144" s="17" t="s">
         <v>373</v>
@@ -4046,7 +4046,7 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B150" s="17" t="s">
         <v>292</v>
@@ -4066,7 +4066,7 @@
     </row>
     <row r="152" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B152" s="18" t="s">
         <v>288</v>
@@ -4083,25 +4083,25 @@
     <row r="155" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A156" s="92" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B156" s="88" t="s">
         <v>284</v>
       </c>
-      <c r="C156" s="98" t="s">
-        <v>406</v>
-      </c>
-      <c r="D156" s="100" t="s">
-        <v>406</v>
+      <c r="C156" s="104" t="s">
+        <v>405</v>
+      </c>
+      <c r="D156" s="102" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A157" s="93"/>
       <c r="B157" s="90" t="s">
-        <v>441</v>
-      </c>
-      <c r="C157" s="99"/>
-      <c r="D157" s="101"/>
+        <v>440</v>
+      </c>
+      <c r="C157" s="105"/>
+      <c r="D157" s="103"/>
     </row>
     <row r="158" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A158" s="24" t="s">
@@ -4127,10 +4127,10 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="B160" s="17" t="s">
         <v>430</v>
-      </c>
-      <c r="B160" s="17" t="s">
-        <v>431</v>
       </c>
       <c r="C160" s="5"/>
       <c r="D160" s="8"/>
@@ -4147,7 +4147,7 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B162" s="17" t="s">
         <v>338</v>
@@ -4157,20 +4157,20 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B163" s="17" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C163" s="5"/>
       <c r="D163" s="8"/>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B164" s="17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C164" s="5"/>
       <c r="D164" s="8"/>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A168" s="35" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B168" s="36" t="s">
         <v>340</v>
@@ -4211,7 +4211,7 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A169" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B169" s="17" t="s">
         <v>341</v>
@@ -4249,7 +4249,7 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B173" s="17" t="s">
         <v>291</v>
@@ -4279,17 +4279,17 @@
     </row>
     <row r="176" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A176" s="50" t="s">
+        <v>445</v>
+      </c>
+      <c r="B176" s="51" t="s">
         <v>375</v>
-      </c>
-      <c r="B176" s="51" t="s">
-        <v>376</v>
       </c>
       <c r="C176" s="11"/>
       <c r="D176" s="9"/>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B178" s="32" t="s">
         <v>337</v>
@@ -4301,10 +4301,10 @@
         <v>372</v>
       </c>
       <c r="B180" s="84" t="s">
+        <v>411</v>
+      </c>
+      <c r="C180" s="25" t="s">
         <v>412</v>
-      </c>
-      <c r="C180" s="25" t="s">
-        <v>413</v>
       </c>
       <c r="D180" s="29"/>
     </row>
@@ -4384,7 +4384,7 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B189" s="17" t="s">
         <v>371</v>
@@ -4439,7 +4439,7 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A195" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B195" s="17" t="s">
         <v>374</v>
@@ -4457,7 +4457,7 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A197" s="35" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B197" s="36" t="s">
         <v>342</v>
@@ -4497,10 +4497,10 @@
     </row>
     <row r="201" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A201" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="B201" s="51" t="s">
         <v>377</v>
-      </c>
-      <c r="B201" s="51" t="s">
-        <v>378</v>
       </c>
       <c r="C201" s="52"/>
       <c r="D201" s="53"/>
@@ -4521,18 +4521,18 @@
       <c r="B205" s="88" t="s">
         <v>354</v>
       </c>
-      <c r="C205" s="98" t="s">
-        <v>406</v>
-      </c>
-      <c r="D205" s="96"/>
+      <c r="C205" s="104" t="s">
+        <v>405</v>
+      </c>
+      <c r="D205" s="106"/>
     </row>
     <row r="206" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A206" s="93"/>
       <c r="B206" s="90" t="s">
-        <v>442</v>
-      </c>
-      <c r="C206" s="99"/>
-      <c r="D206" s="97"/>
+        <v>441</v>
+      </c>
+      <c r="C206" s="105"/>
+      <c r="D206" s="107"/>
     </row>
     <row r="207" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A207" s="24" t="s">
@@ -4598,7 +4598,7 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A213" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B213" s="17" t="s">
         <v>333</v>
@@ -4608,7 +4608,7 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A214" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B214" s="17" t="s">
         <v>334</v>
@@ -4702,20 +4702,20 @@
         <v>159</v>
       </c>
       <c r="B227" s="88" t="s">
-        <v>445</v>
-      </c>
-      <c r="C227" s="94" t="s">
+        <v>444</v>
+      </c>
+      <c r="C227" s="108" t="s">
         <v>358</v>
       </c>
-      <c r="D227" s="96"/>
+      <c r="D227" s="106"/>
     </row>
     <row r="228" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A228" s="93"/>
       <c r="B228" s="90" t="s">
-        <v>444</v>
-      </c>
-      <c r="C228" s="95"/>
-      <c r="D228" s="97"/>
+        <v>443</v>
+      </c>
+      <c r="C228" s="109"/>
+      <c r="D228" s="107"/>
     </row>
     <row r="229" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A229" s="24" t="s">
@@ -4737,7 +4737,7 @@
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A231" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B231" s="17" t="s">
         <v>316</v>
@@ -4747,7 +4747,7 @@
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A232" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B232" s="17" t="s">
         <v>317</v>
@@ -4797,7 +4797,7 @@
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A237" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B237" s="17" t="s">
         <v>323</v>
@@ -4807,7 +4807,7 @@
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A238" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B238" s="17" t="s">
         <v>305</v>
@@ -4865,7 +4865,7 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A244" s="35" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B244" s="17" t="s">
         <v>328</v>
@@ -4875,10 +4875,10 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A245" s="35" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B245" s="17" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C245" s="46"/>
       <c r="D245" s="45"/>
@@ -4893,7 +4893,7 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A247" s="35" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B247" s="17" t="s">
         <v>346</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A251" s="35" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B251" s="17" t="s">
         <v>350</v>
@@ -4943,7 +4943,7 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A252" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B252" s="17" t="s">
         <v>351</v>
@@ -4953,7 +4953,7 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A253" s="35" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B253" s="17" t="s">
         <v>352</v>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="254" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A254" s="50" t="s">
+        <v>432</v>
+      </c>
+      <c r="B254" s="18" t="s">
         <v>433</v>
-      </c>
-      <c r="B254" s="18" t="s">
-        <v>434</v>
       </c>
       <c r="C254" s="52"/>
       <c r="D254" s="53"/>
@@ -4988,18 +4988,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="D91:D92"/>
-    <mergeCell ref="A131:A132"/>
-    <mergeCell ref="C131:C132"/>
-    <mergeCell ref="D131:D132"/>
     <mergeCell ref="A227:A228"/>
     <mergeCell ref="C227:C228"/>
     <mergeCell ref="D227:D228"/>
@@ -5009,6 +4997,18 @@
     <mergeCell ref="A205:A206"/>
     <mergeCell ref="C205:C206"/>
     <mergeCell ref="D205:D206"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="D91:D92"/>
+    <mergeCell ref="A131:A132"/>
+    <mergeCell ref="C131:C132"/>
+    <mergeCell ref="D131:D132"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
